--- a/public/templates/請求書振込.xlsx
+++ b/public/templates/請求書振込.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/各種資料　原本/請求書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/各種資料　原本/請求書/アプリ用テンプレ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{490BA829-FA41-49C2-9522-0F48835986A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F74B21CD-AFD0-4643-8115-0B3E64690349}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{490BA829-FA41-49C2-9522-0F48835986A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D15762A-F7E3-412B-B35B-C715C988DA20}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5209DA7A-5152-4F99-B3B1-55AC7DC7D125}"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <r>
       <t>請求書</t>
@@ -281,63 +281,12 @@
     <t>合計</t>
   </si>
   <si>
-    <t>任意代理人　月額管理 金銭管理　郵便管理</t>
-    <rPh sb="11" eb="13">
-      <t>キンセン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ユウビン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>有料老人ホーム　サンライフ東駅</t>
-    <rPh sb="0" eb="4">
-      <t>ユウリョウロウジン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒガシエキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>齋藤俊子</t>
-    <rPh sb="0" eb="2">
-      <t>サイトウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トシコ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>有料道路　470円</t>
     <rPh sb="0" eb="4">
       <t>ユウリョウドウロ</t>
     </rPh>
     <rPh sb="8" eb="9">
       <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>土地代支払い代行</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>野村整形同行</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>診察代立替</t>
-    <rPh sb="0" eb="5">
-      <t>シンサツダイタテカエ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -1698,9 +1647,7 @@
       <c r="F2" s="33"/>
       <c r="G2" s="34"/>
       <c r="H2" s="35"/>
-      <c r="I2" s="17" t="s">
-        <v>22</v>
-      </c>
+      <c r="I2" s="17"/>
       <c r="J2" s="37"/>
       <c r="K2" s="37"/>
       <c r="L2" s="37"/>
@@ -1711,7 +1658,7 @@
     </row>
     <row r="3" spans="1:20" ht="21.75" customHeight="1">
       <c r="A3" s="38" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -1731,7 +1678,7 @@
     </row>
     <row r="4" spans="1:20" ht="14.25" customHeight="1">
       <c r="A4" s="38" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
@@ -1751,7 +1698,7 @@
     </row>
     <row r="5" spans="1:20" ht="41.25" customHeight="1">
       <c r="A5" s="42" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
@@ -1760,18 +1707,16 @@
       <c r="F5" s="43"/>
       <c r="G5" s="43"/>
       <c r="H5" s="41"/>
-      <c r="I5" s="28" t="s">
-        <v>23</v>
-      </c>
+      <c r="I5" s="28"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
       <c r="M5" s="45" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N5" s="45">
         <f>I13</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" s="46" t="s">
         <v>1</v>
@@ -1872,7 +1817,7 @@
     <row r="11" spans="1:20" s="2" customFormat="1" ht="27" customHeight="1">
       <c r="A11" s="62">
         <f>O29</f>
-        <v>20230</v>
+        <v>0</v>
       </c>
       <c r="B11" s="63"/>
       <c r="C11" s="63"/>
@@ -1881,17 +1826,15 @@
       <c r="F11" s="64"/>
       <c r="G11" s="50"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="96" t="str">
+      <c r="I11" s="96">
         <f>I5</f>
-        <v>齋藤俊子</v>
+        <v>0</v>
       </c>
       <c r="J11" s="65"/>
       <c r="K11" s="65"/>
       <c r="L11" s="65"/>
       <c r="M11" s="65"/>
-      <c r="N11" s="16">
-        <v>46204</v>
-      </c>
+      <c r="N11" s="16"/>
       <c r="O11" s="66"/>
     </row>
     <row r="12" spans="1:20" ht="10.5" customHeight="1">
@@ -1927,9 +1870,7 @@
       <c r="H13" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="3">
-        <v>6</v>
-      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="72" t="s">
         <v>8</v>
       </c>
@@ -1975,14 +1916,10 @@
       </c>
     </row>
     <row r="15" spans="1:20" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="13">
-        <v>46174</v>
-      </c>
+      <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="D15" s="25"/>
       <c r="E15" s="77"/>
       <c r="F15" s="77"/>
       <c r="G15" s="77"/>
@@ -1996,19 +1933,13 @@
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="27"/>
-      <c r="O15" s="19">
-        <v>1900</v>
-      </c>
+      <c r="O15" s="19"/>
     </row>
     <row r="16" spans="1:20" ht="21" customHeight="1">
-      <c r="A16" s="13">
-        <v>46175</v>
-      </c>
+      <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="25" t="s">
-        <v>26</v>
-      </c>
+      <c r="D16" s="25"/>
       <c r="E16" s="77"/>
       <c r="F16" s="77"/>
       <c r="G16" s="77"/>
@@ -2022,17 +1953,13 @@
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="27"/>
-      <c r="O16" s="19">
-        <v>12500</v>
-      </c>
+      <c r="O16" s="19"/>
     </row>
     <row r="17" spans="1:25" ht="21" customHeight="1">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="D17" s="25"/>
       <c r="E17" s="77"/>
       <c r="F17" s="77"/>
       <c r="G17" s="77"/>
@@ -2046,9 +1973,7 @@
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="27"/>
-      <c r="O17" s="19">
-        <v>1360</v>
-      </c>
+      <c r="O17" s="19"/>
     </row>
     <row r="18" spans="1:25" ht="21" customHeight="1">
       <c r="A18" s="13"/>
@@ -2195,7 +2120,7 @@
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
       <c r="D25" s="25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E25" s="77"/>
       <c r="F25" s="77"/>
@@ -2204,23 +2129,19 @@
       <c r="I25" s="77"/>
       <c r="J25" s="77"/>
       <c r="K25" s="78"/>
-      <c r="L25" s="22">
-        <v>1</v>
-      </c>
+      <c r="L25" s="22"/>
       <c r="M25" s="22"/>
       <c r="N25" s="27"/>
       <c r="O25" s="19">
         <f>470*L25</f>
-        <v>470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="21" customHeight="1">
       <c r="A26" s="20"/>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="25" t="s">
-        <v>21</v>
-      </c>
+      <c r="D26" s="25"/>
       <c r="E26" s="77"/>
       <c r="F26" s="77"/>
       <c r="G26" s="77"/>
@@ -2231,9 +2152,7 @@
       <c r="L26" s="22"/>
       <c r="M26" s="22"/>
       <c r="N26" s="27"/>
-      <c r="O26" s="19">
-        <v>4000</v>
-      </c>
+      <c r="O26" s="19"/>
     </row>
     <row r="27" spans="1:25" ht="21" customHeight="1">
       <c r="A27" s="80"/>
@@ -2254,7 +2173,7 @@
       <c r="N27" s="85"/>
       <c r="O27" s="79">
         <f>O29-O28</f>
-        <v>18870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="21" customHeight="1">
@@ -2276,7 +2195,7 @@
       <c r="N28" s="88"/>
       <c r="O28" s="79">
         <f>O17+O24</f>
-        <v>1360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="21" customHeight="1">
@@ -2298,7 +2217,7 @@
       <c r="N29" s="90"/>
       <c r="O29" s="91">
         <f>SUM(O15:O26)</f>
-        <v>20230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1">
@@ -2309,7 +2228,7 @@
       <c r="E30" s="92"/>
       <c r="F30" s="92"/>
       <c r="G30" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H30" s="92"/>
       <c r="I30" s="92"/>
@@ -2347,7 +2266,7 @@
       <c r="F32" s="61"/>
       <c r="G32" s="61"/>
       <c r="H32" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="6"/>
@@ -2395,7 +2314,7 @@
       <c r="F34" s="104"/>
       <c r="G34" s="104"/>
       <c r="H34" s="11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I34" s="11"/>
       <c r="J34" s="6"/>
@@ -2418,12 +2337,12 @@
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
       <c r="F35" s="100" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G35" s="104"/>
       <c r="H35" s="100"/>
       <c r="I35" s="100" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J35" s="100"/>
       <c r="N35" s="12"/>
@@ -2441,7 +2360,7 @@
     <row r="36" spans="1:33" ht="27" customHeight="1">
       <c r="A36" s="105"/>
       <c r="B36" s="102" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C36" s="102"/>
       <c r="F36" s="106"/>
@@ -2474,11 +2393,11 @@
     </row>
     <row r="37" spans="1:33" ht="13.5" customHeight="1">
       <c r="B37" s="102" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C37" s="102"/>
       <c r="K37" s="102" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L37" s="102"/>
       <c r="M37" s="102"/>
@@ -2499,13 +2418,13 @@
     </row>
     <row r="38" spans="1:33" ht="15" customHeight="1">
       <c r="B38" s="102" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C38" s="102"/>
       <c r="D38" s="102"/>
       <c r="E38" s="102"/>
       <c r="K38" s="102" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L38" s="102"/>
       <c r="M38" s="102"/>
@@ -2519,13 +2438,13 @@
     </row>
     <row r="39" spans="1:33" ht="13.5" customHeight="1">
       <c r="B39" s="102" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C39" s="102"/>
       <c r="D39" s="102"/>
       <c r="E39" s="102"/>
       <c r="K39" s="102" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L39" s="102"/>
       <c r="M39" s="102"/>
@@ -2540,7 +2459,7 @@
     <row r="40" spans="1:33">
       <c r="A40" s="102"/>
       <c r="B40" s="102" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C40" s="102"/>
       <c r="D40" s="102"/>
@@ -2551,7 +2470,7 @@
       <c r="I40" s="102"/>
       <c r="J40" s="102"/>
       <c r="K40" s="102" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L40" s="102"/>
       <c r="M40" s="102"/>
@@ -2596,10 +2515,10 @@
     <row r="42" spans="1:33">
       <c r="A42" s="102"/>
       <c r="B42" s="102" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C42" s="102" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D42" s="102"/>
       <c r="E42" s="102"/>
@@ -2627,7 +2546,7 @@
       <c r="A43" s="102"/>
       <c r="B43" s="102"/>
       <c r="C43" s="102" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D43" s="102"/>
       <c r="E43" s="102"/>
